--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24188-2024 artfynd.xlsx
+++ b/artfynd/A 24188-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>122260945</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
